--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T14:30:40+00:00</t>
+    <t>2024-12-13T08:39:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA (https://www.elga.gv.at/)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:50:04+00:00</t>
+    <t>2025-02-13T14:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="143">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/moped-ext-fehlerWarnung</t>
+    <t>https://elga.moped.at/StructureDefinition/moped-ext-fehlerWarnung</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -132,7 +132,10 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFRequest#Claim</t>
+  </si>
+  <si>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFResponse#ClaimResponse</t>
   </si>
   <si>
     <t>ID</t>
@@ -603,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -770,6 +773,14 @@
       </c>
       <c r="B21" t="s" s="2">
         <v>38</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -822,115 +833,115 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" hidden="true">
@@ -946,10 +957,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -961,7 +972,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1021,16 +1032,16 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1038,10 +1049,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1049,10 +1060,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1064,13 +1075,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1121,41 +1132,41 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1167,16 +1178,16 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1214,58 +1225,58 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>20</v>
@@ -1274,13 +1285,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1331,19 +1342,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1351,10 +1362,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1362,10 +1373,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1377,13 +1388,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1434,30 +1445,30 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1465,10 +1476,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1480,13 +1491,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1525,31 +1536,31 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1557,10 +1568,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1568,10 +1579,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1583,16 +1594,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1600,7 +1611,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>20</v>
@@ -1642,13 +1653,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1657,15 +1668,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1673,10 +1684,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1688,13 +1699,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1745,46 +1756,46 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -1793,13 +1804,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1850,19 +1861,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -1870,10 +1881,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1881,10 +1892,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -1896,13 +1907,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1953,30 +1964,30 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1984,10 +1995,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -1999,13 +2010,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2044,31 +2055,31 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2076,10 +2087,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2087,10 +2098,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2102,16 +2113,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2119,7 +2130,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2161,13 +2172,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -2176,15 +2187,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2192,10 +2203,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2207,13 +2218,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2264,46 +2275,46 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -2312,13 +2323,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2369,19 +2380,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -2389,10 +2400,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2400,10 +2411,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2415,13 +2426,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2472,30 +2483,30 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2503,10 +2514,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2518,13 +2529,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2563,31 +2574,31 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -2595,10 +2606,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2606,10 +2617,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2621,16 +2632,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2638,7 +2649,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>20</v>
@@ -2680,13 +2691,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -2695,15 +2706,15 @@
         <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2711,10 +2722,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2726,13 +2737,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2783,30 +2794,30 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2814,10 +2825,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2829,16 +2840,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2888,13 +2899,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -2903,15 +2914,15 @@
         <v>20</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2919,10 +2930,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -2934,13 +2945,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2991,22 +3002,22 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-fehlerWarnung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
